--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -2433,7 +2433,7 @@
         <v>동행 서비스 제공</v>
       </c>
       <c r="G61" t="str">
-        <v>집에서 출발하여 병원 전 일정 동행 후 집으로 귀가하여 종료</v>
+        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
       </c>
       <c r="H61" t="str">
         <v/>

--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -2241,7 +2241,7 @@
         <v>이용 시간</v>
       </c>
       <c r="G55" t="str">
-        <v>평일 오전 9시~오후 6시 (주말·공휴일 이용 불가)</v>
+        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
       </c>
       <c r="H55" t="str">
         <v>clock</v>
@@ -2561,7 +2561,7 @@
         <v>동행 내용</v>
       </c>
       <c r="G65" t="str">
-        <v>병원 출발 및 귀가 시 동행</v>
+        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2593,7 +2593,7 @@
         <v>동행 내용</v>
       </c>
       <c r="G66" t="str">
-        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행</v>
+        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2625,7 +2625,7 @@
         <v>동행 내용</v>
       </c>
       <c r="G67" t="str">
-        <v>시장·관공서·은행·이미용실 등 일상 동행</v>
+        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
       </c>
       <c r="H67" t="str">
         <v/>

--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -2189,7 +2189,7 @@
         <v/>
       </c>
     </row>
-    <row r="54">
+    <row r="54" xml:space="preserve">
       <c r="A54" t="str">
         <v>O</v>
       </c>
@@ -2208,8 +2208,9 @@
       <c r="F54" t="str">
         <v>이용 대상</v>
       </c>
-      <c r="G54" t="str">
-        <v>원주시에 거주(강원도민) 중인 65세 이상 재가 어르신(요양원, 요양병원 입소자 이용 불가)</v>
+      <c r="G54" t="str" xml:space="preserve">
+        <v xml:space="preserve">원주시에 거주(강원도민) 중인 65세 이상 재가 어르신
+(요양원, 요양병원 입소자 이용 불가)</v>
       </c>
       <c r="H54" t="str">
         <v>user</v>

--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J78"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -929,7 +929,7 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>선배시민봉사단</v>
+        <v>북원보듬 선배시민봉사단</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -1057,7 +1057,7 @@
         <v>문의</v>
       </c>
       <c r="G18" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>지역복지팀 033-747-0516</v>
       </c>
       <c r="H18" t="str">
         <v>phone</v>
@@ -1121,7 +1121,7 @@
         <v>솔선봉사단</v>
       </c>
       <c r="G20" t="str">
-        <v>온기식당 배식 보조 및 이용자 안내</v>
+        <v>'솔선수범' 한다는 의미로 복지관 온기식당에서 배식봉사 및 이용자 편의 안내</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1153,7 +1153,7 @@
         <v>러브레드봉사단</v>
       </c>
       <c r="G21" t="str">
-        <v>제과제빵 지역사회 나눔 및 체험교실 운영</v>
+        <v>'빵으로 사랑을 전달' 한다는 의미로 지역사회 제과제빵 나눔 및 체험교실 운영</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1182,10 +1182,10 @@
         <v>내용</v>
       </c>
       <c r="F22" t="str">
-        <v>지원 근거</v>
+        <v>미소봉사단</v>
       </c>
       <c r="G22" t="str">
-        <v>보건복지부·한국노인종합복지관협회 '2025 노인자원봉사활성화지원사업' 연계</v>
+        <v>'미디어 소통'의 줄임말로 복지관과 어르신의 이야기를 방송으로 전달</v>
       </c>
       <c r="H22" t="str">
         <v/>
@@ -1208,16 +1208,16 @@
         <v/>
       </c>
       <c r="D23" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E23" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F23" t="str">
-        <v/>
+        <v>선배시민 활동</v>
       </c>
       <c r="G23" t="str">
-        <v>교통안전 베테랑 교실</v>
+        <v>선배시민으로서 지역사회와 선배 후배세대를 위한 정책 제안 활동과 선배시민정책대회 운영, 노인권익캠페인 진행</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1240,16 +1240,16 @@
         <v/>
       </c>
       <c r="D24" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E24" t="str">
-        <v>설명</v>
+        <v>내용</v>
       </c>
       <c r="F24" t="str">
-        <v/>
+        <v>지원근거</v>
       </c>
       <c r="G24" t="str">
-        <v>고령자 교통안전 인식개선을 위한 안전운전 교육 및 실습을 진행합니다.</v>
+        <v>보건복지부·한국노인종합복지관협회 '2026 노인자원봉사활성화지원사업' 연계</v>
       </c>
       <c r="H24" t="str">
         <v/>
@@ -1272,19 +1272,19 @@
         <v/>
       </c>
       <c r="D25" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E25" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F25" t="str">
-        <v>이용 대상</v>
+        <v>노인권익캠페인</v>
       </c>
       <c r="G25" t="str">
-        <v>복지관 이용회원 30명 (1기수당 15명)</v>
+        <v>KakaoTalk_20260829_094050035_01.jpg</v>
       </c>
       <c r="H25" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1304,19 +1304,19 @@
         <v/>
       </c>
       <c r="D26" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E26" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F26" t="str">
-        <v>일정</v>
+        <v>선배시민정책대회</v>
       </c>
       <c r="G26" t="str">
-        <v>6~8월</v>
+        <v>DSC03394.JPG</v>
       </c>
       <c r="H26" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1336,22 +1336,22 @@
         <v/>
       </c>
       <c r="D27" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E27" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F27" t="str">
-        <v>문의</v>
+        <v>선배시민정책대회</v>
       </c>
       <c r="G27" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>KakaoTalk_20261008_163848159_24.jpg</v>
       </c>
       <c r="H27" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -1371,13 +1371,13 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E28" t="str">
-        <v>내용제목</v>
+        <v>부제</v>
       </c>
       <c r="F28" t="str">
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>사업 안내</v>
+        <v>교통안전 베테랑 교실</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1403,13 +1403,13 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E29" t="str">
-        <v>내용</v>
+        <v>설명</v>
       </c>
       <c r="F29" t="str">
-        <v>안전운전교육</v>
+        <v/>
       </c>
       <c r="G29" t="str">
-        <v>신체 나이 테스트, 운전습관 점검</v>
+        <v>고령자 교통안전 인식개선을 위한 안전운전 교육 및 실습을 진행합니다.</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1435,16 +1435,16 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E30" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F30" t="str">
-        <v>안전운전교육</v>
+        <v>이용 대상</v>
       </c>
       <c r="G30" t="str">
-        <v>개정된 도로교통법 알아보기 / 고령 운전자 교통사고 특성 이해 / 운전능력 자가진단평가</v>
+        <v>복지관 이용회원 30명 (1기수당 15명)</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1467,16 +1467,16 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E31" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F31" t="str">
-        <v>안전주행실습</v>
+        <v>일정</v>
       </c>
       <c r="G31" t="str">
-        <v>방어 및 안전운전 방법(장애물 회피, 방어운전 등)</v>
+        <v>6~8월</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1499,19 +1499,19 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E32" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F32" t="str">
-        <v>나눔서포터즈</v>
+        <v>문의</v>
       </c>
       <c r="G32" t="str">
-        <v>교통안전 취약지역 모니터링 및 온라인 안전맵핑 게시 / 인식개선 캠페인 / 홍보 영상 제작</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1531,13 +1531,13 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E33" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F33" t="str">
-        <v>지원 근거</v>
+        <v/>
       </c>
       <c r="G33" t="str">
-        <v>한국노인종합복지관협회 '2025 교통안전 베테랑 교실' 선정 / 현대자동차그룹·사회복지공동모금회 지원</v>
+        <v>사업 안내</v>
       </c>
       <c r="H33" t="str">
         <v/>
@@ -1560,16 +1560,16 @@
         <v/>
       </c>
       <c r="D34" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E34" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F34" t="str">
-        <v/>
+        <v>안전운전교육</v>
       </c>
       <c r="G34" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v>신체 나이 테스트, 운전습관 점검</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1592,16 +1592,16 @@
         <v/>
       </c>
       <c r="D35" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E35" t="str">
-        <v>설명</v>
+        <v>내용</v>
       </c>
       <c r="F35" t="str">
-        <v/>
+        <v>안전운전교육</v>
       </c>
       <c r="G35" t="str">
-        <v>신노년층 대상 액티브시니어의 생활양식 기반 웰에이징 교육을 진행하여 노인복지증진 및 지역사회 내 통합적 공동체 발전에 기여합니다.</v>
+        <v>개정된 도로교통법 알아보기 / 고령 운전자 교통사고 특성 이해 / 운전능력 자가진단평가</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1624,19 +1624,19 @@
         <v/>
       </c>
       <c r="D36" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E36" t="str">
-        <v>정보</v>
+        <v>내용</v>
       </c>
       <c r="F36" t="str">
-        <v>이용 대상</v>
+        <v>안전주행실습</v>
       </c>
       <c r="G36" t="str">
-        <v>복지관 이용회원 15명</v>
+        <v>방어 및 안전운전 방법(장애물 회피, 방어운전 등)</v>
       </c>
       <c r="H36" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1656,19 +1656,19 @@
         <v/>
       </c>
       <c r="D37" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E37" t="str">
-        <v>정보</v>
+        <v>내용</v>
       </c>
       <c r="F37" t="str">
-        <v>일정</v>
+        <v>나눔서포터즈</v>
       </c>
       <c r="G37" t="str">
-        <v>6월~12월</v>
+        <v>교통안전 취약지역 모니터링 및 온라인 안전맵핑 게시 / 인식개선 캠페인 / 홍보 영상 제작</v>
       </c>
       <c r="H37" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1688,22 +1688,22 @@
         <v/>
       </c>
       <c r="D38" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E38" t="str">
-        <v>정보</v>
+        <v>내용</v>
       </c>
       <c r="F38" t="str">
-        <v>문의</v>
+        <v>지원 근거</v>
       </c>
       <c r="G38" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>한국노인종합복지관협회 '2025 교통안전 베테랑 교실' 선정 / 현대자동차그룹·사회복지공동모금회 지원</v>
       </c>
       <c r="H38" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I38" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J38" t="str">
         <v/>
@@ -1723,13 +1723,13 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E39" t="str">
-        <v>내용제목</v>
+        <v>부제</v>
       </c>
       <c r="F39" t="str">
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>사업 안내</v>
+        <v>BRAVO, MY LIFE!</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -1755,13 +1755,13 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E40" t="str">
-        <v>내용</v>
+        <v>설명</v>
       </c>
       <c r="F40" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v/>
       </c>
       <c r="G40" t="str">
-        <v>경제(Bankable)·관계(Relation)·활동(Active)·가치소비(Value consumption)·사회적 역할(Occupation) 교육</v>
+        <v>신노년층 대상 액티브시니어의 생활양식 기반 웰에이징 교육을 진행하여 노인복지증진 및 지역사회 내 통합적 공동체 발전에 기여합니다.</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1787,16 +1787,16 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E41" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F41" t="str">
-        <v>지원 근거</v>
+        <v>이용 대상</v>
       </c>
       <c r="G41" t="str">
-        <v>강원특별자치도청 '2024 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
+        <v>복지관 이용회원 15명</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1816,19 +1816,19 @@
         <v/>
       </c>
       <c r="D42" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E42" t="str">
-        <v>부제</v>
+        <v>정보</v>
       </c>
       <c r="F42" t="str">
-        <v/>
+        <v>일정</v>
       </c>
       <c r="G42" t="str">
-        <v>방송 진행자 교육</v>
+        <v>6월~12월</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1848,22 +1848,22 @@
         <v/>
       </c>
       <c r="D43" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E43" t="str">
-        <v>설명</v>
+        <v>정보</v>
       </c>
       <c r="F43" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G43" t="str">
-        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -1880,19 +1880,19 @@
         <v/>
       </c>
       <c r="D44" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E44" t="str">
-        <v>정보</v>
+        <v>내용제목</v>
       </c>
       <c r="F44" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G44" t="str">
-        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>사업 안내</v>
       </c>
       <c r="H44" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1912,19 +1912,19 @@
         <v/>
       </c>
       <c r="D45" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E45" t="str">
-        <v>정보</v>
+        <v>내용</v>
       </c>
       <c r="F45" t="str">
-        <v>일정</v>
+        <v>BRAVO, MY LIFE!</v>
       </c>
       <c r="G45" t="str">
-        <v>3~6월</v>
+        <v>경제(Bankable)·관계(Relation)·활동(Active)·가치소비(Value consumption)·사회적 역할(Occupation) 교육</v>
       </c>
       <c r="H45" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1944,22 +1944,22 @@
         <v/>
       </c>
       <c r="D46" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E46" t="str">
-        <v>정보</v>
+        <v>내용</v>
       </c>
       <c r="F46" t="str">
-        <v>문의</v>
+        <v>지원 근거</v>
       </c>
       <c r="G46" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>강원특별자치도청 '2024 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
       </c>
       <c r="H46" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I46" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J46" t="str">
         <v/>
@@ -1979,13 +1979,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E47" t="str">
-        <v>내용제목</v>
+        <v>부제</v>
       </c>
       <c r="F47" t="str">
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>사업 내용</v>
+        <v>방송 진행자 교육</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2011,13 +2011,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E48" t="str">
-        <v>내용</v>
+        <v>설명</v>
       </c>
       <c r="F48" t="str">
-        <v>보이는 라디오란?</v>
+        <v/>
       </c>
       <c r="G48" t="str">
-        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
+        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -2043,16 +2043,16 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E49" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F49" t="str">
-        <v>보이는 라디오 방송 실습</v>
+        <v>이용 대상</v>
       </c>
       <c r="G49" t="str">
-        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
+        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2075,16 +2075,16 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E50" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F50" t="str">
-        <v>조별 방송 제작</v>
+        <v>일정</v>
       </c>
       <c r="G50" t="str">
-        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
+        <v>3~6월</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2107,19 +2107,19 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E51" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F51" t="str">
-        <v>지원 근거</v>
+        <v>문의</v>
       </c>
       <c r="G51" t="str">
-        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+        <v>복지사업팀 033-747-0516</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2136,16 +2136,16 @@
         <v/>
       </c>
       <c r="D52" t="str">
-        <v>원주시어르신병원동행서비스</v>
+        <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E52" t="str">
-        <v>부제</v>
+        <v>내용제목</v>
       </c>
       <c r="F52" t="str">
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
+        <v>사업 내용</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -2168,212 +2168,212 @@
         <v/>
       </c>
       <c r="D53" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E53" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F53" t="str">
+        <v>보이는 라디오란?</v>
+      </c>
+      <c r="G53" t="str">
+        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>O</v>
+      </c>
+      <c r="B54" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C54" t="str">
+        <v/>
+      </c>
+      <c r="D54" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E54" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F54" t="str">
+        <v>보이는 라디오 방송 실습</v>
+      </c>
+      <c r="G54" t="str">
+        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>O</v>
+      </c>
+      <c r="B55" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C55" t="str">
+        <v/>
+      </c>
+      <c r="D55" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E55" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F55" t="str">
+        <v>조별 방송 제작</v>
+      </c>
+      <c r="G55" t="str">
+        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>O</v>
+      </c>
+      <c r="B56" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C56" t="str">
+        <v/>
+      </c>
+      <c r="D56" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E56" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F56" t="str">
+        <v>지원 근거</v>
+      </c>
+      <c r="G56" t="str">
+        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>O</v>
+      </c>
+      <c r="B57" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C57" t="str">
+        <v/>
+      </c>
+      <c r="D57" t="str">
         <v>원주시어르신병원동행서비스</v>
       </c>
-      <c r="E53" t="str">
+      <c r="E57" t="str">
+        <v>부제</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>O</v>
+      </c>
+      <c r="B58" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C58" t="str">
+        <v/>
+      </c>
+      <c r="D58" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E58" t="str">
         <v>설명</v>
       </c>
-      <c r="F53" t="str">
-        <v/>
-      </c>
-      <c r="G53" t="str">
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
         <v>전문 동행 매니저의 보호자 역할로 믿고 안심할 수 있는 병원 이용 및 일상생활을 지원하여 보호자 부담을 경감하고 노인 돌봄을 강화합니다.</v>
       </c>
-      <c r="H53" t="str">
-        <v/>
-      </c>
-      <c r="I53" t="str">
-        <v/>
-      </c>
-      <c r="J53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str">
-        <v>O</v>
-      </c>
-      <c r="B54" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C54" t="str">
-        <v/>
-      </c>
-      <c r="D54" t="str">
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59" xml:space="preserve">
+      <c r="A59" t="str">
+        <v>O</v>
+      </c>
+      <c r="B59" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C59" t="str">
+        <v/>
+      </c>
+      <c r="D59" t="str">
         <v>원주시어르신병원동행서비스</v>
       </c>
-      <c r="E54" t="str">
+      <c r="E59" t="str">
         <v>정보</v>
       </c>
-      <c r="F54" t="str">
+      <c r="F59" t="str">
         <v>이용 대상</v>
       </c>
-      <c r="G54" t="str" xml:space="preserve">
+      <c r="G59" t="str" xml:space="preserve">
         <v xml:space="preserve">원주시에 거주(강원도민) 중인 65세 이상 재가 어르신
 (요양원, 요양병원 입소자 이용 불가)</v>
       </c>
-      <c r="H54" t="str">
+      <c r="H59" t="str">
         <v>user</v>
-      </c>
-      <c r="I54" t="str">
-        <v/>
-      </c>
-      <c r="J54" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>O</v>
-      </c>
-      <c r="B55" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E55" t="str">
-        <v>정보</v>
-      </c>
-      <c r="F55" t="str">
-        <v>이용 시간</v>
-      </c>
-      <c r="G55" t="str">
-        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
-      </c>
-      <c r="H55" t="str">
-        <v>clock</v>
-      </c>
-      <c r="I55" t="str">
-        <v/>
-      </c>
-      <c r="J55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>O</v>
-      </c>
-      <c r="B56" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C56" t="str">
-        <v/>
-      </c>
-      <c r="D56" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E56" t="str">
-        <v>정보</v>
-      </c>
-      <c r="F56" t="str">
-        <v>문의</v>
-      </c>
-      <c r="G56" t="str">
-        <v>북원노인종합복지관 033-747-8899</v>
-      </c>
-      <c r="H56" t="str">
-        <v>phone</v>
-      </c>
-      <c r="I56" t="str">
-        <v>033-747-8899</v>
-      </c>
-      <c r="J56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>O</v>
-      </c>
-      <c r="B57" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C57" t="str">
-        <v/>
-      </c>
-      <c r="D57" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E57" t="str">
-        <v>절차제목</v>
-      </c>
-      <c r="F57" t="str">
-        <v/>
-      </c>
-      <c r="G57" t="str">
-        <v>서비스 진행 과정</v>
-      </c>
-      <c r="H57" t="str">
-        <v/>
-      </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
-      <c r="J57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>O</v>
-      </c>
-      <c r="B58" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E58" t="str">
-        <v>절차</v>
-      </c>
-      <c r="F58" t="str">
-        <v>서비스 신청</v>
-      </c>
-      <c r="G58" t="str">
-        <v>최소 1주일 전 신청(예약제로 운영)</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v/>
-      </c>
-      <c r="J58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>O</v>
-      </c>
-      <c r="B59" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C59" t="str">
-        <v/>
-      </c>
-      <c r="D59" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E59" t="str">
-        <v>절차</v>
-      </c>
-      <c r="F59" t="str">
-        <v>담당자 방문 상담</v>
-      </c>
-      <c r="G59" t="str">
-        <v>최초 1회</v>
-      </c>
-      <c r="H59" t="str">
-        <v/>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2396,16 +2396,16 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E60" t="str">
-        <v>절차</v>
+        <v>정보</v>
       </c>
       <c r="F60" t="str">
-        <v>동행 매니저 매칭</v>
+        <v>이용 시간</v>
       </c>
       <c r="G60" t="str">
-        <v/>
+        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2428,19 +2428,19 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E61" t="str">
-        <v>절차</v>
+        <v>정보</v>
       </c>
       <c r="F61" t="str">
-        <v>동행 서비스 제공</v>
+        <v>문의</v>
       </c>
       <c r="G61" t="str">
-        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
+        <v>북원노인종합복지관 033-747-8899</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>033-747-8899</v>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2460,13 +2460,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E62" t="str">
-        <v>절차</v>
+        <v>절차제목</v>
       </c>
       <c r="F62" t="str">
-        <v>비용 수납</v>
+        <v/>
       </c>
       <c r="G62" t="str">
-        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
+        <v>서비스 진행 과정</v>
       </c>
       <c r="H62" t="str">
         <v/>
@@ -2492,13 +2492,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E63" t="str">
-        <v>안내</v>
+        <v>절차</v>
       </c>
       <c r="F63" t="str">
-        <v/>
+        <v>서비스 신청</v>
       </c>
       <c r="G63" t="str">
-        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
+        <v>최소 1주일 전 신청(예약제로 운영)</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2524,13 +2524,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E64" t="str">
-        <v>내용제목</v>
+        <v>절차</v>
       </c>
       <c r="F64" t="str">
-        <v/>
+        <v>담당자 방문 상담</v>
       </c>
       <c r="G64" t="str">
-        <v>서비스 내용</v>
+        <v>최초 1회</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -2556,13 +2556,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E65" t="str">
-        <v>내용</v>
+        <v>절차</v>
       </c>
       <c r="F65" t="str">
-        <v>동행 내용</v>
+        <v>동행 매니저 매칭</v>
       </c>
       <c r="G65" t="str">
-        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
+        <v/>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2588,13 +2588,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E66" t="str">
-        <v>내용</v>
+        <v>절차</v>
       </c>
       <c r="F66" t="str">
-        <v>동행 내용</v>
+        <v>동행 서비스 제공</v>
       </c>
       <c r="G66" t="str">
-        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
+        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2620,13 +2620,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E67" t="str">
-        <v>내용</v>
+        <v>절차</v>
       </c>
       <c r="F67" t="str">
-        <v>동행 내용</v>
+        <v>비용 수납</v>
       </c>
       <c r="G67" t="str">
-        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
+        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2652,13 +2652,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E68" t="str">
-        <v>내용</v>
+        <v>안내</v>
       </c>
       <c r="F68" t="str">
-        <v>이용요금</v>
+        <v/>
       </c>
       <c r="G68" t="str">
-        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
+        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2684,13 +2684,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E69" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F69" t="str">
-        <v>이용요금</v>
+        <v/>
       </c>
       <c r="G69" t="str">
-        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
+        <v>서비스 내용</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2716,13 +2716,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E70" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>동행 내용</v>
       </c>
       <c r="G70" t="str">
-        <v>전산월4.jpg</v>
+        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -2748,13 +2748,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E71" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F71" t="str">
-        <v/>
+        <v>동행 내용</v>
       </c>
       <c r="G71" t="str">
-        <v>박상주1.jpg</v>
+        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -2780,13 +2780,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E72" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F72" t="str">
-        <v/>
+        <v>동행 내용</v>
       </c>
       <c r="G72" t="str">
-        <v>라현자2.jpg</v>
+        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -2812,27 +2812,187 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E73" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F73" t="str">
+        <v>이용요금</v>
+      </c>
+      <c r="G73" t="str">
+        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>O</v>
+      </c>
+      <c r="B74" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C74" t="str">
+        <v/>
+      </c>
+      <c r="D74" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E74" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F74" t="str">
+        <v>이용요금</v>
+      </c>
+      <c r="G74" t="str">
+        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>O</v>
+      </c>
+      <c r="B75" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C75" t="str">
+        <v/>
+      </c>
+      <c r="D75" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E75" t="str">
         <v>사진</v>
       </c>
-      <c r="F73" t="str">
-        <v/>
-      </c>
-      <c r="G73" t="str">
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>전산월4.jpg</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>O</v>
+      </c>
+      <c r="B76" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C76" t="str">
+        <v/>
+      </c>
+      <c r="D76" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E76" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>박상주1.jpg</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>O</v>
+      </c>
+      <c r="B77" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C77" t="str">
+        <v/>
+      </c>
+      <c r="D77" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E77" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>라현자2.jpg</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>O</v>
+      </c>
+      <c r="B78" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C78" t="str">
+        <v/>
+      </c>
+      <c r="D78" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E78" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
         <v>KakaoTalk_20260612_110801162_01.jpg</v>
       </c>
-      <c r="H73" t="str">
-        <v/>
-      </c>
-      <c r="I73" t="str">
-        <v/>
-      </c>
-      <c r="J73" t="str">
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J73"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J78"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1368,16 +1368,16 @@
         <v/>
       </c>
       <c r="D28" t="str">
-        <v>교통안전베테랑교실지원사업</v>
+        <v>노인자원봉사활성화지원사업</v>
       </c>
       <c r="E28" t="str">
-        <v>부제</v>
+        <v>사진</v>
       </c>
       <c r="F28" t="str">
-        <v/>
+        <v>선배시민정책콘서트</v>
       </c>
       <c r="G28" t="str">
-        <v>교통안전 베테랑 교실</v>
+        <v>단체사진.JPG</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1403,13 +1403,13 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E29" t="str">
-        <v>설명</v>
+        <v>부제</v>
       </c>
       <c r="F29" t="str">
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>고령자 교통안전 인식개선을 위한 안전운전 교육 및 실습을 진행합니다.</v>
+        <v>교통안전 베테랑 교실</v>
       </c>
       <c r="H29" t="str">
         <v/>
@@ -1435,16 +1435,16 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E30" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F30" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G30" t="str">
-        <v>복지관 이용회원 30명 (1기수당 15명)</v>
+        <v>고령자 교통안전 인식개선을 위한 안전운전 교육 및 실습을 진행합니다.</v>
       </c>
       <c r="H30" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1470,13 +1470,13 @@
         <v>정보</v>
       </c>
       <c r="F31" t="str">
-        <v>일정</v>
+        <v>이용 대상</v>
       </c>
       <c r="G31" t="str">
-        <v>6~8월</v>
+        <v>복지관 이용회원 30명 (1기수당 15명)</v>
       </c>
       <c r="H31" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1502,16 +1502,16 @@
         <v>정보</v>
       </c>
       <c r="F32" t="str">
-        <v>문의</v>
+        <v>일정</v>
       </c>
       <c r="G32" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>6~8월</v>
       </c>
       <c r="H32" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I32" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -1531,19 +1531,19 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E33" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F33" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G33" t="str">
-        <v>사업 안내</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J33" t="str">
         <v/>
@@ -1563,13 +1563,13 @@
         <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E34" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F34" t="str">
-        <v>안전운전교육</v>
+        <v/>
       </c>
       <c r="G34" t="str">
-        <v>신체 나이 테스트, 운전습관 점검</v>
+        <v>사업 안내</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1601,7 +1601,7 @@
         <v>안전운전교육</v>
       </c>
       <c r="G35" t="str">
-        <v>개정된 도로교통법 알아보기 / 고령 운전자 교통사고 특성 이해 / 운전능력 자가진단평가</v>
+        <v>신체 나이 테스트, 운전습관 점검</v>
       </c>
       <c r="H35" t="str">
         <v/>
@@ -1630,10 +1630,10 @@
         <v>내용</v>
       </c>
       <c r="F36" t="str">
-        <v>안전주행실습</v>
+        <v>안전운전교육</v>
       </c>
       <c r="G36" t="str">
-        <v>방어 및 안전운전 방법(장애물 회피, 방어운전 등)</v>
+        <v>개정된 도로교통법 알아보기 / 고령 운전자 교통사고 특성 이해 / 운전능력 자가진단평가</v>
       </c>
       <c r="H36" t="str">
         <v/>
@@ -1662,10 +1662,10 @@
         <v>내용</v>
       </c>
       <c r="F37" t="str">
-        <v>나눔서포터즈</v>
+        <v>안전주행실습</v>
       </c>
       <c r="G37" t="str">
-        <v>교통안전 취약지역 모니터링 및 온라인 안전맵핑 게시 / 인식개선 캠페인 / 홍보 영상 제작</v>
+        <v>방어 및 안전운전 방법(장애물 회피, 방어운전 등)</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1694,10 +1694,10 @@
         <v>내용</v>
       </c>
       <c r="F38" t="str">
-        <v>지원 근거</v>
+        <v>나눔서포터즈</v>
       </c>
       <c r="G38" t="str">
-        <v>한국노인종합복지관협회 '2025 교통안전 베테랑 교실' 선정 / 현대자동차그룹·사회복지공동모금회 지원</v>
+        <v>교통안전 취약지역 모니터링 및 온라인 안전맵핑 게시 / 인식개선 캠페인 / 홍보 영상 제작</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -1720,16 +1720,16 @@
         <v/>
       </c>
       <c r="D39" t="str">
-        <v>강원특별자치도노인복지증진사업</v>
+        <v>교통안전베테랑교실지원사업</v>
       </c>
       <c r="E39" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F39" t="str">
-        <v/>
+        <v>지원 근거</v>
       </c>
       <c r="G39" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v>한국노인종합복지관협회 '2025 교통안전 베테랑 교실' 선정 / 현대자동차그룹·사회복지공동모금회 지원</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -1755,13 +1755,13 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E40" t="str">
-        <v>설명</v>
+        <v>부제</v>
       </c>
       <c r="F40" t="str">
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>신노년층 대상 액티브시니어의 생활양식 기반 웰에이징 교육을 진행하여 노인복지증진 및 지역사회 내 통합적 공동체 발전에 기여합니다.</v>
+        <v>BRAVO, MY LIFE!</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1787,16 +1787,16 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E41" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F41" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G41" t="str">
-        <v>복지관 이용회원 15명</v>
+        <v>신노년층 대상 액티브시니어의 생활양식 기반 웰에이징 교육을 진행하여 노인복지증진 및 지역사회 내 통합적 공동체 발전에 기여합니다.</v>
       </c>
       <c r="H41" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1822,13 +1822,13 @@
         <v>정보</v>
       </c>
       <c r="F42" t="str">
-        <v>일정</v>
+        <v>이용 대상</v>
       </c>
       <c r="G42" t="str">
-        <v>6월~12월</v>
+        <v>복지관 이용회원 15명</v>
       </c>
       <c r="H42" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1854,16 +1854,16 @@
         <v>정보</v>
       </c>
       <c r="F43" t="str">
-        <v>문의</v>
+        <v>일정</v>
       </c>
       <c r="G43" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>6월~12월</v>
       </c>
       <c r="H43" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I43" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J43" t="str">
         <v/>
@@ -1883,19 +1883,19 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E44" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F44" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G44" t="str">
-        <v>사업 안내</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J44" t="str">
         <v/>
@@ -1915,13 +1915,13 @@
         <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E45" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F45" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v/>
       </c>
       <c r="G45" t="str">
-        <v>경제(Bankable)·관계(Relation)·활동(Active)·가치소비(Value consumption)·사회적 역할(Occupation) 교육</v>
+        <v>사업 안내</v>
       </c>
       <c r="H45" t="str">
         <v/>
@@ -1950,10 +1950,10 @@
         <v>내용</v>
       </c>
       <c r="F46" t="str">
-        <v>지원 근거</v>
+        <v>BRAVO, MY LIFE!</v>
       </c>
       <c r="G46" t="str">
-        <v>강원특별자치도청 '2024 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
+        <v>경제(Bankable)·관계(Relation)·활동(Active)·가치소비(Value consumption)·사회적 역할(Occupation) 교육</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1976,16 +1976,16 @@
         <v/>
       </c>
       <c r="D47" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E47" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F47" t="str">
-        <v/>
+        <v>지원 근거</v>
       </c>
       <c r="G47" t="str">
-        <v>방송 진행자 교육</v>
+        <v>강원특별자치도청 '2024 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2011,13 +2011,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E48" t="str">
-        <v>설명</v>
+        <v>부제</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
+        <v>방송 진행자 교육</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -2043,16 +2043,16 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E49" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F49" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G49" t="str">
-        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
       </c>
       <c r="H49" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2078,13 +2078,13 @@
         <v>정보</v>
       </c>
       <c r="F50" t="str">
-        <v>일정</v>
+        <v>이용 대상</v>
       </c>
       <c r="G50" t="str">
-        <v>3~6월</v>
+        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H50" t="str">
-        <v>clock</v>
+        <v>user</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2110,16 +2110,16 @@
         <v>정보</v>
       </c>
       <c r="F51" t="str">
-        <v>문의</v>
+        <v>일정</v>
       </c>
       <c r="G51" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>3~6월</v>
       </c>
       <c r="H51" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I51" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -2139,19 +2139,19 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E52" t="str">
-        <v>내용제목</v>
+        <v>정보</v>
       </c>
       <c r="F52" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G52" t="str">
-        <v>사업 내용</v>
+        <v>복지사업팀 033-747-0516</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2171,13 +2171,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E53" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F53" t="str">
-        <v>보이는 라디오란?</v>
+        <v/>
       </c>
       <c r="G53" t="str">
-        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
+        <v>사업 내용</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -2206,10 +2206,10 @@
         <v>내용</v>
       </c>
       <c r="F54" t="str">
-        <v>보이는 라디오 방송 실습</v>
+        <v>보이는 라디오란?</v>
       </c>
       <c r="G54" t="str">
-        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
+        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2238,10 +2238,10 @@
         <v>내용</v>
       </c>
       <c r="F55" t="str">
-        <v>조별 방송 제작</v>
+        <v>보이는 라디오 방송 실습</v>
       </c>
       <c r="G55" t="str">
-        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
+        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
       </c>
       <c r="H55" t="str">
         <v/>
@@ -2270,10 +2270,10 @@
         <v>내용</v>
       </c>
       <c r="F56" t="str">
-        <v>지원 근거</v>
+        <v>조별 방송 제작</v>
       </c>
       <c r="G56" t="str">
-        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2296,16 +2296,16 @@
         <v/>
       </c>
       <c r="D57" t="str">
-        <v>원주시어르신병원동행서비스</v>
+        <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E57" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F57" t="str">
-        <v/>
+        <v>지원 근거</v>
       </c>
       <c r="G57" t="str">
-        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
+        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2331,13 +2331,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E58" t="str">
-        <v>설명</v>
+        <v>부제</v>
       </c>
       <c r="F58" t="str">
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>전문 동행 매니저의 보호자 역할로 믿고 안심할 수 있는 병원 이용 및 일상생활을 지원하여 보호자 부담을 경감하고 노인 돌봄을 강화합니다.</v>
+        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -2349,7 +2349,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" xml:space="preserve">
+    <row r="59">
       <c r="A59" t="str">
         <v>O</v>
       </c>
@@ -2363,49 +2363,49 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E59" t="str">
+        <v>설명</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>전문 동행 매니저의 보호자 역할로 믿고 안심할 수 있는 병원 이용 및 일상생활을 지원하여 보호자 부담을 경감하고 노인 돌봄을 강화합니다.</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60" xml:space="preserve">
+      <c r="A60" t="str">
+        <v>O</v>
+      </c>
+      <c r="B60" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E60" t="str">
         <v>정보</v>
       </c>
-      <c r="F59" t="str">
+      <c r="F60" t="str">
         <v>이용 대상</v>
       </c>
-      <c r="G59" t="str" xml:space="preserve">
+      <c r="G60" t="str" xml:space="preserve">
         <v xml:space="preserve">원주시에 거주(강원도민) 중인 65세 이상 재가 어르신
 (요양원, 요양병원 입소자 이용 불가)</v>
       </c>
-      <c r="H59" t="str">
+      <c r="H60" t="str">
         <v>user</v>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>O</v>
-      </c>
-      <c r="B60" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E60" t="str">
-        <v>정보</v>
-      </c>
-      <c r="F60" t="str">
-        <v>이용 시간</v>
-      </c>
-      <c r="G60" t="str">
-        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
-      </c>
-      <c r="H60" t="str">
-        <v>clock</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2431,16 +2431,16 @@
         <v>정보</v>
       </c>
       <c r="F61" t="str">
-        <v>문의</v>
+        <v>이용 시간</v>
       </c>
       <c r="G61" t="str">
-        <v>북원노인종합복지관 033-747-8899</v>
+        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
       </c>
       <c r="H61" t="str">
-        <v>phone</v>
+        <v>clock</v>
       </c>
       <c r="I61" t="str">
-        <v>033-747-8899</v>
+        <v/>
       </c>
       <c r="J61" t="str">
         <v/>
@@ -2460,19 +2460,19 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E62" t="str">
-        <v>절차제목</v>
+        <v>정보</v>
       </c>
       <c r="F62" t="str">
-        <v/>
+        <v>문의</v>
       </c>
       <c r="G62" t="str">
-        <v>서비스 진행 과정</v>
+        <v>북원노인종합복지관 033-747-8899</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>033-747-8899</v>
       </c>
       <c r="J62" t="str">
         <v/>
@@ -2492,13 +2492,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E63" t="str">
-        <v>절차</v>
+        <v>절차제목</v>
       </c>
       <c r="F63" t="str">
-        <v>서비스 신청</v>
+        <v/>
       </c>
       <c r="G63" t="str">
-        <v>최소 1주일 전 신청(예약제로 운영)</v>
+        <v>서비스 진행 과정</v>
       </c>
       <c r="H63" t="str">
         <v/>
@@ -2527,10 +2527,10 @@
         <v>절차</v>
       </c>
       <c r="F64" t="str">
-        <v>담당자 방문 상담</v>
+        <v>서비스 신청</v>
       </c>
       <c r="G64" t="str">
-        <v>최초 1회</v>
+        <v>최소 1주일 전 신청(예약제로 운영)</v>
       </c>
       <c r="H64" t="str">
         <v/>
@@ -2559,10 +2559,10 @@
         <v>절차</v>
       </c>
       <c r="F65" t="str">
-        <v>동행 매니저 매칭</v>
+        <v>담당자 방문 상담</v>
       </c>
       <c r="G65" t="str">
-        <v/>
+        <v>최초 1회</v>
       </c>
       <c r="H65" t="str">
         <v/>
@@ -2591,10 +2591,10 @@
         <v>절차</v>
       </c>
       <c r="F66" t="str">
-        <v>동행 서비스 제공</v>
+        <v>동행 매니저 매칭</v>
       </c>
       <c r="G66" t="str">
-        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
+        <v/>
       </c>
       <c r="H66" t="str">
         <v/>
@@ -2623,10 +2623,10 @@
         <v>절차</v>
       </c>
       <c r="F67" t="str">
-        <v>비용 수납</v>
+        <v>동행 서비스 제공</v>
       </c>
       <c r="G67" t="str">
-        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
+        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2652,13 +2652,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E68" t="str">
-        <v>안내</v>
+        <v>절차</v>
       </c>
       <c r="F68" t="str">
-        <v/>
+        <v>비용 수납</v>
       </c>
       <c r="G68" t="str">
-        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
+        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2684,13 +2684,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E69" t="str">
-        <v>내용제목</v>
+        <v>안내</v>
       </c>
       <c r="F69" t="str">
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>서비스 내용</v>
+        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2716,13 +2716,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E70" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F70" t="str">
-        <v>동행 내용</v>
+        <v/>
       </c>
       <c r="G70" t="str">
-        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
+        <v>서비스 내용</v>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -2754,7 +2754,7 @@
         <v>동행 내용</v>
       </c>
       <c r="G71" t="str">
-        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
+        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -2786,7 +2786,7 @@
         <v>동행 내용</v>
       </c>
       <c r="G72" t="str">
-        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
+        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -2815,10 +2815,10 @@
         <v>내용</v>
       </c>
       <c r="F73" t="str">
-        <v>이용요금</v>
+        <v>동행 내용</v>
       </c>
       <c r="G73" t="str">
-        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
+        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -2850,7 +2850,7 @@
         <v>이용요금</v>
       </c>
       <c r="G74" t="str">
-        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
+        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -2876,13 +2876,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E75" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F75" t="str">
-        <v/>
+        <v>이용요금</v>
       </c>
       <c r="G75" t="str">
-        <v>전산월4.jpg</v>
+        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -2914,7 +2914,7 @@
         <v/>
       </c>
       <c r="G76" t="str">
-        <v>박상주1.jpg</v>
+        <v>전산월4.jpg</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -2946,7 +2946,7 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>라현자2.jpg</v>
+        <v>박상주1.jpg</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -2978,21 +2978,53 @@
         <v/>
       </c>
       <c r="G78" t="str">
+        <v>라현자2.jpg</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>O</v>
+      </c>
+      <c r="B79" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C79" t="str">
+        <v/>
+      </c>
+      <c r="D79" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E79" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
         <v>KakaoTalk_20260612_110801162_01.jpg</v>
       </c>
-      <c r="H78" t="str">
-        <v/>
-      </c>
-      <c r="I78" t="str">
-        <v/>
-      </c>
-      <c r="J78" t="str">
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v/>
+      </c>
+      <c r="J79" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J78"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J79"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J79"/>
+  <dimension ref="A1:J89"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3022,9 +3022,329 @@
         <v/>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>O</v>
+      </c>
+      <c r="B80" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C80" t="str">
+        <v/>
+      </c>
+      <c r="D80" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E80" t="str">
+        <v>설명</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>황혼육아 역량강화를 위한 정서·신체·관계·교육 통합 지원 프로그램 “함께 자람”</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>O</v>
+      </c>
+      <c r="B81" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C81" t="str">
+        <v/>
+      </c>
+      <c r="D81" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E81" t="str">
+        <v>부제</v>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>황혼육아지원사업</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>O</v>
+      </c>
+      <c r="B82" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C82" t="str">
+        <v/>
+      </c>
+      <c r="D82" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E82" t="str">
+        <v>정보</v>
+      </c>
+      <c r="F82" t="str">
+        <v>이용대상</v>
+      </c>
+      <c r="G82" t="str">
+        <v>만0세 이상 7세 이하 손자녀를 양육 중인 복지관 회원</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>O</v>
+      </c>
+      <c r="B83" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C83" t="str">
+        <v/>
+      </c>
+      <c r="D83" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E83" t="str">
+        <v>정보</v>
+      </c>
+      <c r="F83" t="str">
+        <v>일정</v>
+      </c>
+      <c r="G83" t="str">
+        <v>3월~9월</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>O</v>
+      </c>
+      <c r="B84" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C84" t="str">
+        <v/>
+      </c>
+      <c r="D84" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E84" t="str">
+        <v>정보</v>
+      </c>
+      <c r="F84" t="str">
+        <v>문의</v>
+      </c>
+      <c r="G84" t="str">
+        <v>문화사업팀 033-747-0516</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v>033-747-0516</v>
+      </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>O</v>
+      </c>
+      <c r="B85" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C85" t="str">
+        <v/>
+      </c>
+      <c r="D85" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E85" t="str">
+        <v>내용제목</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>사업 안내</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>O</v>
+      </c>
+      <c r="B86" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C86" t="str">
+        <v/>
+      </c>
+      <c r="D86" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E86" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F86" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G86" t="str">
+        <v>모금회_1.jpg</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v/>
+      </c>
+      <c r="J86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>O</v>
+      </c>
+      <c r="B87" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C87" t="str">
+        <v/>
+      </c>
+      <c r="D87" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E87" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F87" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G87" t="str">
+        <v>모금회_3.jpg</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>O</v>
+      </c>
+      <c r="B88" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C88" t="str">
+        <v/>
+      </c>
+      <c r="D88" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E88" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F88" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G88" t="str">
+        <v>모금회_4.jpg</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>O</v>
+      </c>
+      <c r="B89" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C89" t="str">
+        <v/>
+      </c>
+      <c r="D89" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E89" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F89" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G89" t="str">
+        <v>모금회.jpg</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J79"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J93"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1761,7 +1761,7 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v>「하나비 프로젝트」: 무대너머 지역을 잇-다</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1793,7 +1793,7 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>신노년층 대상 액티브시니어의 생활양식 기반 웰에이징 교육을 진행하여 노인복지증진 및 지역사회 내 통합적 공동체 발전에 기여합니다.</v>
+        <v>참여형 음악활동을 매개로 긍정적 노인 인식과 고령친화적 사회통합 환경 조성을 도모합니다.</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1825,7 +1825,7 @@
         <v>이용 대상</v>
       </c>
       <c r="G42" t="str">
-        <v>복지관 이용회원 15명</v>
+        <v>복지관 이용 회원 중 외부 공연단50명</v>
       </c>
       <c r="H42" t="str">
         <v>user</v>
@@ -1857,7 +1857,7 @@
         <v>일정</v>
       </c>
       <c r="G43" t="str">
-        <v>6월~12월</v>
+        <v>1월~12월</v>
       </c>
       <c r="H43" t="str">
         <v>clock</v>
@@ -1950,10 +1950,10 @@
         <v>내용</v>
       </c>
       <c r="F46" t="str">
-        <v>BRAVO, MY LIFE!</v>
+        <v>하나비 프로젝트</v>
       </c>
       <c r="G46" t="str">
-        <v>경제(Bankable)·관계(Relation)·활동(Active)·가치소비(Value consumption)·사회적 역할(Occupation) 교육</v>
+        <v>[4D 전략] 형성(Deifine), 성장(Develop), 나눔(Distribute), 확산(Diffuse)</v>
       </c>
       <c r="H46" t="str">
         <v/>
@@ -1985,7 +1985,7 @@
         <v>지원 근거</v>
       </c>
       <c r="G47" t="str">
-        <v>강원특별자치도청 '2024 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
+        <v>강원특별자치도청 '2026 강원특별자치도 노인복지증진사업 공모사업' 선정</v>
       </c>
       <c r="H47" t="str">
         <v/>
@@ -2008,16 +2008,16 @@
         <v/>
       </c>
       <c r="D48" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E48" t="str">
-        <v>부제</v>
+        <v>사진</v>
       </c>
       <c r="F48" t="str">
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>방송 진행자 교육</v>
+        <v>하나비_1.jpg</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -2040,16 +2040,16 @@
         <v/>
       </c>
       <c r="D49" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E49" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F49" t="str">
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
+        <v>하나비_2.jpg</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -2072,19 +2072,19 @@
         <v/>
       </c>
       <c r="D50" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E50" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F50" t="str">
-        <v>이용 대상</v>
+        <v/>
       </c>
       <c r="G50" t="str">
-        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
+        <v>하나비_3.jpg</v>
       </c>
       <c r="H50" t="str">
-        <v>user</v>
+        <v/>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2104,19 +2104,19 @@
         <v/>
       </c>
       <c r="D51" t="str">
-        <v>찾아가는미디어교육지원사업</v>
+        <v>강원특별자치도노인복지증진사업</v>
       </c>
       <c r="E51" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F51" t="str">
-        <v>일정</v>
+        <v/>
       </c>
       <c r="G51" t="str">
-        <v>3~6월</v>
+        <v>하나비.jpg</v>
       </c>
       <c r="H51" t="str">
-        <v>clock</v>
+        <v/>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2139,19 +2139,19 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E52" t="str">
-        <v>정보</v>
+        <v>부제</v>
       </c>
       <c r="F52" t="str">
-        <v>문의</v>
+        <v/>
       </c>
       <c r="G52" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>방송 진행자 교육</v>
       </c>
       <c r="H52" t="str">
-        <v>phone</v>
+        <v/>
       </c>
       <c r="I52" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J52" t="str">
         <v/>
@@ -2171,13 +2171,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E53" t="str">
-        <v>내용제목</v>
+        <v>설명</v>
       </c>
       <c r="F53" t="str">
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>사업 내용</v>
+        <v>북원우리방송국에서 공개방송(보이는 라디오)을 제작·진행할 수 있는 역량을 함양하고, 시니어의 디지털 격차를 해소합니다.</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -2203,16 +2203,16 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E54" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F54" t="str">
-        <v>보이는 라디오란?</v>
+        <v>이용 대상</v>
       </c>
       <c r="G54" t="str">
-        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
+        <v>방송 제작·프로그램 참여를 희망하는 복지관 이용 회원</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>user</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2235,16 +2235,16 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E55" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F55" t="str">
-        <v>보이는 라디오 방송 실습</v>
+        <v>일정</v>
       </c>
       <c r="G55" t="str">
-        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
+        <v>3~6월</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2267,19 +2267,19 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E56" t="str">
-        <v>내용</v>
+        <v>정보</v>
       </c>
       <c r="F56" t="str">
-        <v>조별 방송 제작</v>
+        <v>문의</v>
       </c>
       <c r="G56" t="str">
-        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
+        <v>복지사업팀 033-747-0516</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -2299,13 +2299,13 @@
         <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E57" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F57" t="str">
-        <v>지원 근거</v>
+        <v/>
       </c>
       <c r="G57" t="str">
-        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+        <v>사업 내용</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2328,16 +2328,16 @@
         <v/>
       </c>
       <c r="D58" t="str">
-        <v>원주시어르신병원동행서비스</v>
+        <v>찾아가는미디어교육지원사업</v>
       </c>
       <c r="E58" t="str">
-        <v>부제</v>
+        <v>내용</v>
       </c>
       <c r="F58" t="str">
-        <v/>
+        <v>보이는 라디오란?</v>
       </c>
       <c r="G58" t="str">
-        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
+        <v>보이는 라디오 공개 방송의 필요성과 효과성에 대한 이론 교육</v>
       </c>
       <c r="H58" t="str">
         <v/>
@@ -2360,180 +2360,180 @@
         <v/>
       </c>
       <c r="D59" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E59" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F59" t="str">
+        <v>보이는 라디오 방송 실습</v>
+      </c>
+      <c r="G59" t="str">
+        <v>방송 큐시트(대본) 작성, 올바른 발음·발성법 연습, 인터뷰 해보기</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>O</v>
+      </c>
+      <c r="B60" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C60" t="str">
+        <v/>
+      </c>
+      <c r="D60" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E60" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F60" t="str">
+        <v>조별 방송 제작</v>
+      </c>
+      <c r="G60" t="str">
+        <v>조별 공개 방송 제작 / 복지관 소식·건강 상식·체조·신청곡·사연 소개 방송</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>O</v>
+      </c>
+      <c r="B61" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C61" t="str">
+        <v/>
+      </c>
+      <c r="D61" t="str">
+        <v>찾아가는미디어교육지원사업</v>
+      </c>
+      <c r="E61" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F61" t="str">
+        <v>지원 근거</v>
+      </c>
+      <c r="G61" t="str">
+        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>O</v>
+      </c>
+      <c r="B62" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C62" t="str">
+        <v/>
+      </c>
+      <c r="D62" t="str">
         <v>원주시어르신병원동행서비스</v>
       </c>
-      <c r="E59" t="str">
+      <c r="E62" t="str">
+        <v>부제</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>어르신의 안전한 일상을 위한 동행 서비스</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>O</v>
+      </c>
+      <c r="B63" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C63" t="str">
+        <v/>
+      </c>
+      <c r="D63" t="str">
+        <v>원주시어르신병원동행서비스</v>
+      </c>
+      <c r="E63" t="str">
         <v>설명</v>
       </c>
-      <c r="F59" t="str">
-        <v/>
-      </c>
-      <c r="G59" t="str">
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
         <v>전문 동행 매니저의 보호자 역할로 믿고 안심할 수 있는 병원 이용 및 일상생활을 지원하여 보호자 부담을 경감하고 노인 돌봄을 강화합니다.</v>
       </c>
-      <c r="H59" t="str">
-        <v/>
-      </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
-      <c r="J59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60" xml:space="preserve">
-      <c r="A60" t="str">
-        <v>O</v>
-      </c>
-      <c r="B60" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C60" t="str">
-        <v/>
-      </c>
-      <c r="D60" t="str">
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64" xml:space="preserve">
+      <c r="A64" t="str">
+        <v>O</v>
+      </c>
+      <c r="B64" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C64" t="str">
+        <v/>
+      </c>
+      <c r="D64" t="str">
         <v>원주시어르신병원동행서비스</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E64" t="str">
         <v>정보</v>
       </c>
-      <c r="F60" t="str">
+      <c r="F64" t="str">
         <v>이용 대상</v>
       </c>
-      <c r="G60" t="str" xml:space="preserve">
+      <c r="G64" t="str" xml:space="preserve">
         <v xml:space="preserve">원주시에 거주(강원도민) 중인 65세 이상 재가 어르신
 (요양원, 요양병원 입소자 이용 불가)</v>
       </c>
-      <c r="H60" t="str">
+      <c r="H64" t="str">
         <v>user</v>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-      <c r="J60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>O</v>
-      </c>
-      <c r="B61" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C61" t="str">
-        <v/>
-      </c>
-      <c r="D61" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E61" t="str">
-        <v>정보</v>
-      </c>
-      <c r="F61" t="str">
-        <v>이용 시간</v>
-      </c>
-      <c r="G61" t="str">
-        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
-      </c>
-      <c r="H61" t="str">
-        <v>clock</v>
-      </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>O</v>
-      </c>
-      <c r="B62" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C62" t="str">
-        <v/>
-      </c>
-      <c r="D62" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E62" t="str">
-        <v>정보</v>
-      </c>
-      <c r="F62" t="str">
-        <v>문의</v>
-      </c>
-      <c r="G62" t="str">
-        <v>북원노인종합복지관 033-747-8899</v>
-      </c>
-      <c r="H62" t="str">
-        <v>phone</v>
-      </c>
-      <c r="I62" t="str">
-        <v>033-747-8899</v>
-      </c>
-      <c r="J62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>O</v>
-      </c>
-      <c r="B63" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C63" t="str">
-        <v/>
-      </c>
-      <c r="D63" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E63" t="str">
-        <v>절차제목</v>
-      </c>
-      <c r="F63" t="str">
-        <v/>
-      </c>
-      <c r="G63" t="str">
-        <v>서비스 진행 과정</v>
-      </c>
-      <c r="H63" t="str">
-        <v/>
-      </c>
-      <c r="I63" t="str">
-        <v/>
-      </c>
-      <c r="J63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>O</v>
-      </c>
-      <c r="B64" t="str">
-        <v>jiwon</v>
-      </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="D64" t="str">
-        <v>원주시어르신병원동행서비스</v>
-      </c>
-      <c r="E64" t="str">
-        <v>절차</v>
-      </c>
-      <c r="F64" t="str">
-        <v>서비스 신청</v>
-      </c>
-      <c r="G64" t="str">
-        <v>최소 1주일 전 신청(예약제로 운영)</v>
-      </c>
-      <c r="H64" t="str">
-        <v/>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2556,16 +2556,16 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E65" t="str">
-        <v>절차</v>
+        <v>정보</v>
       </c>
       <c r="F65" t="str">
-        <v>담당자 방문 상담</v>
+        <v>이용 시간</v>
       </c>
       <c r="G65" t="str">
-        <v>최초 1회</v>
+        <v>평일 9시~18시 : 병원 일정에 따라 조정 가능(주말·공휴일 이용은 불가)</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>clock</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2588,19 +2588,19 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E66" t="str">
-        <v>절차</v>
+        <v>정보</v>
       </c>
       <c r="F66" t="str">
-        <v>동행 매니저 매칭</v>
+        <v>문의</v>
       </c>
       <c r="G66" t="str">
-        <v/>
+        <v>북원노인종합복지관 033-747-8899</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>phone</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>033-747-8899</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -2620,13 +2620,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E67" t="str">
-        <v>절차</v>
+        <v>절차제목</v>
       </c>
       <c r="F67" t="str">
-        <v>동행 서비스 제공</v>
+        <v/>
       </c>
       <c r="G67" t="str">
-        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
+        <v>서비스 진행 과정</v>
       </c>
       <c r="H67" t="str">
         <v/>
@@ -2655,10 +2655,10 @@
         <v>절차</v>
       </c>
       <c r="F68" t="str">
-        <v>비용 수납</v>
+        <v>서비스 신청</v>
       </c>
       <c r="G68" t="str">
-        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
+        <v>최소 1주일 전 신청(예약제로 운영)</v>
       </c>
       <c r="H68" t="str">
         <v/>
@@ -2684,13 +2684,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E69" t="str">
-        <v>안내</v>
+        <v>절차</v>
       </c>
       <c r="F69" t="str">
-        <v/>
+        <v>담당자 방문 상담</v>
       </c>
       <c r="G69" t="str">
-        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
+        <v>최초 1회</v>
       </c>
       <c r="H69" t="str">
         <v/>
@@ -2716,13 +2716,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E70" t="str">
-        <v>내용제목</v>
+        <v>절차</v>
       </c>
       <c r="F70" t="str">
-        <v/>
+        <v>동행 매니저 매칭</v>
       </c>
       <c r="G70" t="str">
-        <v>서비스 내용</v>
+        <v/>
       </c>
       <c r="H70" t="str">
         <v/>
@@ -2748,13 +2748,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E71" t="str">
-        <v>내용</v>
+        <v>절차</v>
       </c>
       <c r="F71" t="str">
-        <v>동행 내용</v>
+        <v>동행 서비스 제공</v>
       </c>
       <c r="G71" t="str">
-        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
+        <v>집에서 출발하여 병원 전일정 동행 후 집으로 귀가하여 종료</v>
       </c>
       <c r="H71" t="str">
         <v/>
@@ -2780,13 +2780,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E72" t="str">
-        <v>내용</v>
+        <v>절차</v>
       </c>
       <c r="F72" t="str">
-        <v>동행 내용</v>
+        <v>비용 수납</v>
       </c>
       <c r="G72" t="str">
-        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
+        <v>서비스 종료시 현금 또는 당일 계좌이체</v>
       </c>
       <c r="H72" t="str">
         <v/>
@@ -2812,13 +2812,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E73" t="str">
-        <v>내용</v>
+        <v>안내</v>
       </c>
       <c r="F73" t="str">
-        <v>동행 내용</v>
+        <v/>
       </c>
       <c r="G73" t="str">
-        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
+        <v>이동 수단은 지원하지 않습니다 (택시·버스·교통약자특별교통수단 등 이용, 교통비 자부담).</v>
       </c>
       <c r="H73" t="str">
         <v/>
@@ -2844,13 +2844,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E74" t="str">
-        <v>내용</v>
+        <v>내용제목</v>
       </c>
       <c r="F74" t="str">
-        <v>이용요금</v>
+        <v/>
       </c>
       <c r="G74" t="str">
-        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
+        <v>서비스 내용</v>
       </c>
       <c r="H74" t="str">
         <v/>
@@ -2879,10 +2879,10 @@
         <v>내용</v>
       </c>
       <c r="F75" t="str">
-        <v>이용요금</v>
+        <v>동행 내용</v>
       </c>
       <c r="G75" t="str">
-        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
+        <v>관내·관외(편도 2시간 이내) 병원 출발부터 귀가 시까지 동행</v>
       </c>
       <c r="H75" t="str">
         <v/>
@@ -2908,13 +2908,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E76" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F76" t="str">
-        <v/>
+        <v>동행 내용</v>
       </c>
       <c r="G76" t="str">
-        <v>전산월4.jpg</v>
+        <v>병원 접수·검사·진료·수납·약 처방 수령 등 동행(건강검진 동행도 가능)</v>
       </c>
       <c r="H76" t="str">
         <v/>
@@ -2940,13 +2940,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E77" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F77" t="str">
-        <v/>
+        <v>동행 내용</v>
       </c>
       <c r="G77" t="str">
-        <v>박상주1.jpg</v>
+        <v>시장·은행·관공서·이미용실 등 일상 동행</v>
       </c>
       <c r="H77" t="str">
         <v/>
@@ -2972,13 +2972,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E78" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F78" t="str">
-        <v/>
+        <v>이용요금</v>
       </c>
       <c r="G78" t="str">
-        <v>라현자2.jpg</v>
+        <v>일반: 최초 1시간 5,000원, 추가 30분당 1,500원</v>
       </c>
       <c r="H78" t="str">
         <v/>
@@ -3004,13 +3004,13 @@
         <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E79" t="str">
-        <v>사진</v>
+        <v>내용</v>
       </c>
       <c r="F79" t="str">
-        <v/>
+        <v>이용요금</v>
       </c>
       <c r="G79" t="str">
-        <v>KakaoTalk_20260612_110801162_01.jpg</v>
+        <v>기초생활수급·차상위계층: 최초 1시간 1,000원, 추가 30분당 500원</v>
       </c>
       <c r="H79" t="str">
         <v/>
@@ -3033,16 +3033,16 @@
         <v/>
       </c>
       <c r="D80" t="str">
-        <v>사회복지공동모금회</v>
+        <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E80" t="str">
-        <v>설명</v>
+        <v>사진</v>
       </c>
       <c r="F80" t="str">
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>황혼육아 역량강화를 위한 정서·신체·관계·교육 통합 지원 프로그램 “함께 자람”</v>
+        <v>전산월4.jpg</v>
       </c>
       <c r="H80" t="str">
         <v/>
@@ -3065,16 +3065,16 @@
         <v/>
       </c>
       <c r="D81" t="str">
-        <v>사회복지공동모금회</v>
+        <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E81" t="str">
-        <v>부제</v>
+        <v>사진</v>
       </c>
       <c r="F81" t="str">
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>황혼육아지원사업</v>
+        <v>박상주1.jpg</v>
       </c>
       <c r="H81" t="str">
         <v/>
@@ -3097,16 +3097,16 @@
         <v/>
       </c>
       <c r="D82" t="str">
-        <v>사회복지공동모금회</v>
+        <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E82" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F82" t="str">
-        <v>이용대상</v>
+        <v/>
       </c>
       <c r="G82" t="str">
-        <v>만0세 이상 7세 이하 손자녀를 양육 중인 복지관 회원</v>
+        <v>라현자2.jpg</v>
       </c>
       <c r="H82" t="str">
         <v/>
@@ -3129,16 +3129,16 @@
         <v/>
       </c>
       <c r="D83" t="str">
-        <v>사회복지공동모금회</v>
+        <v>원주시어르신병원동행서비스</v>
       </c>
       <c r="E83" t="str">
-        <v>정보</v>
+        <v>사진</v>
       </c>
       <c r="F83" t="str">
-        <v>일정</v>
+        <v/>
       </c>
       <c r="G83" t="str">
-        <v>3월~9월</v>
+        <v>KakaoTalk_20260612_110801162_01.jpg</v>
       </c>
       <c r="H83" t="str">
         <v/>
@@ -3164,19 +3164,19 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E84" t="str">
-        <v>정보</v>
+        <v>설명</v>
       </c>
       <c r="F84" t="str">
-        <v>문의</v>
+        <v/>
       </c>
       <c r="G84" t="str">
-        <v>문화사업팀 033-747-0516</v>
+        <v>황혼육아 역량강화를 위한 정서·신체·관계·교육 통합 지원 프로그램 “함께 자람”</v>
       </c>
       <c r="H84" t="str">
         <v/>
       </c>
       <c r="I84" t="str">
-        <v>033-747-0516</v>
+        <v/>
       </c>
       <c r="J84" t="str">
         <v/>
@@ -3196,13 +3196,13 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E85" t="str">
-        <v>내용제목</v>
+        <v>부제</v>
       </c>
       <c r="F85" t="str">
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>사업 안내</v>
+        <v>황혼육아지원사업</v>
       </c>
       <c r="H85" t="str">
         <v/>
@@ -3228,13 +3228,13 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E86" t="str">
-        <v>사진</v>
+        <v>정보</v>
       </c>
       <c r="F86" t="str">
-        <v>함께자람</v>
+        <v>이용대상</v>
       </c>
       <c r="G86" t="str">
-        <v>모금회_1.jpg</v>
+        <v>만0세 이상 7세 이하 손자녀를 양육 중인 복지관 회원</v>
       </c>
       <c r="H86" t="str">
         <v/>
@@ -3260,13 +3260,13 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E87" t="str">
-        <v>사진</v>
+        <v>정보</v>
       </c>
       <c r="F87" t="str">
-        <v>함께자람</v>
+        <v>일정</v>
       </c>
       <c r="G87" t="str">
-        <v>모금회_3.jpg</v>
+        <v>3월~9월</v>
       </c>
       <c r="H87" t="str">
         <v/>
@@ -3292,19 +3292,19 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E88" t="str">
-        <v>사진</v>
+        <v>정보</v>
       </c>
       <c r="F88" t="str">
-        <v>함께자람</v>
+        <v>문의</v>
       </c>
       <c r="G88" t="str">
-        <v>모금회_4.jpg</v>
+        <v>문화사업팀 033-747-0516</v>
       </c>
       <c r="H88" t="str">
         <v/>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>033-747-0516</v>
       </c>
       <c r="J88" t="str">
         <v/>
@@ -3324,27 +3324,155 @@
         <v>사회복지공동모금회</v>
       </c>
       <c r="E89" t="str">
+        <v>내용제목</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>사업 안내</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>O</v>
+      </c>
+      <c r="B90" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C90" t="str">
+        <v/>
+      </c>
+      <c r="D90" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E90" t="str">
         <v>사진</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F90" t="str">
         <v>함께자람</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G90" t="str">
+        <v>모금회_1.jpg</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>O</v>
+      </c>
+      <c r="B91" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C91" t="str">
+        <v/>
+      </c>
+      <c r="D91" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E91" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F91" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G91" t="str">
+        <v>모금회_3.jpg</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>O</v>
+      </c>
+      <c r="B92" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C92" t="str">
+        <v/>
+      </c>
+      <c r="D92" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E92" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F92" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G92" t="str">
+        <v>모금회_4.jpg</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>O</v>
+      </c>
+      <c r="B93" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C93" t="str">
+        <v/>
+      </c>
+      <c r="D93" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E93" t="str">
+        <v>사진</v>
+      </c>
+      <c r="F93" t="str">
+        <v>함께자람</v>
+      </c>
+      <c r="G93" t="str">
         <v>모금회.jpg</v>
       </c>
-      <c r="H89" t="str">
-        <v/>
-      </c>
-      <c r="I89" t="str">
-        <v/>
-      </c>
-      <c r="J89" t="str">
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v/>
+      </c>
+      <c r="J93" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J95"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1825,7 +1825,7 @@
         <v>이용 대상</v>
       </c>
       <c r="G42" t="str">
-        <v>복지관 이용 회원 중 외부 공연단50명</v>
+        <v>복지관 이용 회원 중 외부 공연단 50명</v>
       </c>
       <c r="H42" t="str">
         <v>user</v>
@@ -3470,9 +3470,73 @@
         <v/>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>O</v>
+      </c>
+      <c r="B94" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C94" t="str">
+        <v/>
+      </c>
+      <c r="D94" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E94" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F94" t="str">
+        <v>[4H 전략]</v>
+      </c>
+      <c r="G94" t="str">
+        <v>육아교육(Horizons), 정서지원(Heart), 신체지원(Health), 사회관계(harmony)</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>O</v>
+      </c>
+      <c r="B95" t="str">
+        <v>jiwon</v>
+      </c>
+      <c r="C95" t="str">
+        <v/>
+      </c>
+      <c r="D95" t="str">
+        <v>사회복지공동모금회</v>
+      </c>
+      <c r="E95" t="str">
+        <v>내용</v>
+      </c>
+      <c r="F95" t="str">
+        <v>지원 근거</v>
+      </c>
+      <c r="G95" t="str">
+        <v>사회복지공동모금회 '2026년 신청사업(프로그램)' 공모사업' 선정</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -2014,7 +2014,7 @@
         <v>사진</v>
       </c>
       <c r="F48" t="str">
-        <v/>
+        <v>기타 어울림</v>
       </c>
       <c r="G48" t="str">
         <v>하나비_1.jpg</v>
@@ -2046,7 +2046,7 @@
         <v>사진</v>
       </c>
       <c r="F49" t="str">
-        <v/>
+        <v>라인 파플러</v>
       </c>
       <c r="G49" t="str">
         <v>하나비_2.jpg</v>
@@ -2078,7 +2078,7 @@
         <v>사진</v>
       </c>
       <c r="F50" t="str">
-        <v/>
+        <v>알로하 훌라</v>
       </c>
       <c r="G50" t="str">
         <v>하나비_3.jpg</v>
@@ -2110,7 +2110,7 @@
         <v>사진</v>
       </c>
       <c r="F51" t="str">
-        <v/>
+        <v>하모의 꿈</v>
       </c>
       <c r="G51" t="str">
         <v>하나비.jpg</v>

--- a/data/saeop/지원사업.xlsx
+++ b/data/saeop/지원사업.xlsx
@@ -2273,7 +2273,7 @@
         <v>문의</v>
       </c>
       <c r="G56" t="str">
-        <v>복지사업팀 033-747-0516</v>
+        <v>지역복지팀 033-747-0516</v>
       </c>
       <c r="H56" t="str">
         <v>phone</v>
@@ -2433,7 +2433,7 @@
         <v>지원 근거</v>
       </c>
       <c r="G61" t="str">
-        <v>2025 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
+        <v>2026 시청자미디어재단 주관 '찾아가는 미디어교육 지원' 공모사업 선정</v>
       </c>
       <c r="H61" t="str">
         <v/>
